--- a/results/greedy/UAVs6_GRID13/revenue/UAVs6_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs6_GRID13/revenue/UAVs6_GRID13_Greedy.xlsx
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02804629202000797</v>
+        <v>0.0275510840001516</v>
       </c>
       <c r="C2" t="n">
         <v>22.03601984821984</v>
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03690004203235731</v>
+        <v>0.029060082975775</v>
       </c>
       <c r="C2" t="n">
         <v>29.28950278519935</v>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03263229102594778</v>
+        <v>0.02896591601893306</v>
       </c>
       <c r="C2" t="n">
         <v>18.35190168986177</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02573637501336634</v>
+        <v>0.02519029099494219</v>
       </c>
       <c r="C2" t="n">
         <v>23.15638464690869</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0312337499926798</v>
+        <v>0.02998950000619516</v>
       </c>
       <c r="C2" t="n">
         <v>33.65493619585379</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03071870899293572</v>
+        <v>0.03044012497412041</v>
       </c>
       <c r="C2" t="n">
         <v>30.35759085654207</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03055279195541516</v>
+        <v>0.02990545897046104</v>
       </c>
       <c r="C2" t="n">
         <v>30.02368335018279</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02748987497761846</v>
+        <v>0.02715791697846726</v>
       </c>
       <c r="C2" t="n">
         <v>28.82881202592714</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03035270801046863</v>
+        <v>0.02997070801211521</v>
       </c>
       <c r="C2" t="n">
         <v>32.12904001494914</v>
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03298349998658523</v>
+        <v>0.0320966670406051</v>
       </c>
       <c r="C2" t="n">
         <v>22.0618633491888</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02276308299042284</v>
+        <v>0.02213308302452788</v>
       </c>
       <c r="C2" t="n">
         <v>28.25870754107827</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03000529197743163</v>
+        <v>0.02938554203137755</v>
       </c>
       <c r="C2" t="n">
         <v>25.1241342173652</v>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02495524997357279</v>
+        <v>0.02459899999666959</v>
       </c>
       <c r="C2" t="n">
         <v>25.59595959784506</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932979201432317</v>
+        <v>0.02867737499764189</v>
       </c>
       <c r="C2" t="n">
         <v>19.90124277938915</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02864808298181742</v>
+        <v>0.02806012501241639</v>
       </c>
       <c r="C2" t="n">
         <v>18.29892475334922</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03186549997190014</v>
+        <v>0.03133200004231185</v>
       </c>
       <c r="C2" t="n">
         <v>23.35471121474562</v>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02667979203397408</v>
+        <v>0.02627416700124741</v>
       </c>
       <c r="C2" t="n">
         <v>23.14833995101325</v>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02577841700986028</v>
+        <v>0.02515916700940579</v>
       </c>
       <c r="C2" t="n">
         <v>16.79384373948809</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02623550000134856</v>
+        <v>0.02558374998625368</v>
       </c>
       <c r="C2" t="n">
         <v>18.48671267501164</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02418829197995365</v>
+        <v>0.02388908399734646</v>
       </c>
       <c r="C2" t="n">
         <v>23.58000159949182</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02640483301365748</v>
+        <v>0.02579054201487452</v>
       </c>
       <c r="C2" t="n">
         <v>21.82405981796242</v>
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02762520901160315</v>
+        <v>0.02694612502818927</v>
       </c>
       <c r="C2" t="n">
         <v>25.99346061631328</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02939370804233477</v>
+        <v>0.02840050001395866</v>
       </c>
       <c r="C2" t="n">
         <v>24.93305602091468</v>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02317825000500306</v>
+        <v>0.02285841701086611</v>
       </c>
       <c r="C2" t="n">
         <v>21.92307197526525</v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0234663329902105</v>
+        <v>0.02288550004595891</v>
       </c>
       <c r="C2" t="n">
         <v>21.97749828921184</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02456766698742285</v>
+        <v>0.0240295419935137</v>
       </c>
       <c r="C2" t="n">
         <v>17.17916472768112</v>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02583108399994671</v>
+        <v>0.02483004203531891</v>
       </c>
       <c r="C2" t="n">
         <v>24.1167609262199</v>
@@ -2776,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02447958296397701</v>
+        <v>0.02422020799713209</v>
       </c>
       <c r="C2" t="n">
         <v>22.54436730414327</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02587533398764208</v>
+        <v>0.02501554199261591</v>
       </c>
       <c r="C2" t="n">
         <v>17.3115732314635</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02292324998416007</v>
+        <v>0.02251079102279618</v>
       </c>
       <c r="C2" t="n">
         <v>23.73936112239397</v>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03072666696971282</v>
+        <v>0.02998737496091053</v>
       </c>
       <c r="C2" t="n">
         <v>19.73151194935742</v>
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0286375829600729</v>
+        <v>0.02770108298864216</v>
       </c>
       <c r="C2" t="n">
         <v>23.97840807485265</v>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02811579097760841</v>
+        <v>0.02731404203223065</v>
       </c>
       <c r="C2" t="n">
         <v>27.92081469807493</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02057129103923216</v>
+        <v>0.01968445797683671</v>
       </c>
       <c r="C2" t="n">
         <v>21.78805973476554</v>
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02303250000113621</v>
+        <v>0.02241412497824058</v>
       </c>
       <c r="C2" t="n">
         <v>27.24171464813199</v>
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02562670799670741</v>
+        <v>0.02500183403026313</v>
       </c>
       <c r="C2" t="n">
         <v>24.5433041426314</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02507537498604506</v>
+        <v>0.02460491703823209</v>
       </c>
       <c r="C2" t="n">
         <v>22.55873961400847</v>
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03573325002798811</v>
+        <v>0.03423070901772007</v>
       </c>
       <c r="C2" t="n">
         <v>21.6712897109124</v>
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02825245802523568</v>
+        <v>0.0272982909809798</v>
       </c>
       <c r="C2" t="n">
         <v>23.11584874919498</v>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02291500003775582</v>
+        <v>0.02249549998668954</v>
       </c>
       <c r="C2" t="n">
         <v>24.4905058147199</v>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02236175001598895</v>
+        <v>0.02186662500025705</v>
       </c>
       <c r="C2" t="n">
         <v>21.79880306478124</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02779337496031076</v>
+        <v>0.02725995797663927</v>
       </c>
       <c r="C2" t="n">
         <v>18.34277641864116</v>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02225549996364862</v>
+        <v>0.02183670795056969</v>
       </c>
       <c r="C2" t="n">
         <v>17.93794044029475</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03289349999977276</v>
+        <v>0.03245666698785499</v>
       </c>
       <c r="C2" t="n">
         <v>22.35116108760516</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02922941703582183</v>
+        <v>0.02913016703678295</v>
       </c>
       <c r="C2" t="n">
         <v>20.50354395569286</v>
@@ -4252,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03006787499180064</v>
+        <v>0.0291592919966206</v>
       </c>
       <c r="C2" t="n">
         <v>28.61556256222276</v>
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02757241699146107</v>
+        <v>0.02697312500094995</v>
       </c>
       <c r="C2" t="n">
         <v>24.88746867068073</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0240195409860462</v>
+        <v>0.02330291602993384</v>
       </c>
       <c r="C2" t="n">
         <v>24.46830807390545</v>
@@ -4498,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03523837501415983</v>
+        <v>0.03440866596065462</v>
       </c>
       <c r="C2" t="n">
         <v>22.95319995980014</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02294999995501712</v>
+        <v>0.0221745420130901</v>
       </c>
       <c r="C2" t="n">
         <v>21.89647686035734</v>
@@ -4662,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02549579204060137</v>
+        <v>0.02480949996970594</v>
       </c>
       <c r="C2" t="n">
         <v>22.02114914635661</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03239870897959918</v>
+        <v>0.03213399997912347</v>
       </c>
       <c r="C2" t="n">
         <v>20.65073803524404</v>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02118820796022192</v>
+        <v>0.02047841699095443</v>
       </c>
       <c r="C2" t="n">
         <v>23.97437968876231</v>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03296862496063113</v>
+        <v>0.03150616702623665</v>
       </c>
       <c r="C2" t="n">
         <v>18.9863261839787</v>
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02273354097269475</v>
+        <v>0.02212233399040997</v>
       </c>
       <c r="C2" t="n">
         <v>30.07226733260812</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0223595830029808</v>
+        <v>0.02182029199320823</v>
       </c>
       <c r="C2" t="n">
         <v>27.33366989088363</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02914420899469405</v>
+        <v>0.02853287500329316</v>
       </c>
       <c r="C2" t="n">
         <v>28.13257346125701</v>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761366701452062</v>
+        <v>0.0265000420040451</v>
       </c>
       <c r="C2" t="n">
         <v>26.22672285991993</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02441933302907273</v>
+        <v>0.02401812502648681</v>
       </c>
       <c r="C2" t="n">
         <v>19.62577991293459</v>
@@ -5400,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02959287498379126</v>
+        <v>0.02911466598743573</v>
       </c>
       <c r="C2" t="n">
         <v>22.98857844681716</v>
@@ -5482,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02671712497249246</v>
+        <v>0.02613087499048561</v>
       </c>
       <c r="C2" t="n">
         <v>24.19647588320612</v>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0225529579911381</v>
+        <v>0.02203629101859406</v>
       </c>
       <c r="C2" t="n">
         <v>26.58613951306989</v>
@@ -5646,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02911645901622251</v>
+        <v>0.02797604200895876</v>
       </c>
       <c r="C2" t="n">
         <v>21.92262512073578</v>
@@ -5728,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02635658299550414</v>
+        <v>0.02559224999276921</v>
       </c>
       <c r="C2" t="n">
         <v>21.37627224811055</v>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02832637500250712</v>
+        <v>0.02802262495970353</v>
       </c>
       <c r="C2" t="n">
         <v>27.88925930542947</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.018693916965276</v>
+        <v>0.01814066700171679</v>
       </c>
       <c r="C2" t="n">
         <v>19.40025253135037</v>
@@ -5974,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02856537501793355</v>
+        <v>0.02750108402688056</v>
       </c>
       <c r="C2" t="n">
         <v>15.21854064045392</v>
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02650487498613074</v>
+        <v>0.02598204195965081</v>
       </c>
       <c r="C2" t="n">
         <v>22.01653936917196</v>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03212895803153515</v>
+        <v>0.03146958304569125</v>
       </c>
       <c r="C2" t="n">
         <v>19.2609311307482</v>
@@ -6220,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03386441600741819</v>
+        <v>0.03326870797900483</v>
       </c>
       <c r="C2" t="n">
         <v>22.74616692007795</v>
@@ -6302,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03095495799789205</v>
+        <v>0.03029316599713638</v>
       </c>
       <c r="C2" t="n">
         <v>28.75834142897775</v>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03382212499855086</v>
+        <v>0.03341795899905264</v>
       </c>
       <c r="C2" t="n">
         <v>27.68072824292527</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02628645900404081</v>
+        <v>0.02540375001262873</v>
       </c>
       <c r="C2" t="n">
         <v>24.51982953038614</v>
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02387029200326651</v>
+        <v>0.02334874996449798</v>
       </c>
       <c r="C2" t="n">
         <v>15.94961257308852</v>
@@ -6630,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01989799999864772</v>
+        <v>0.01926079200347885</v>
       </c>
       <c r="C2" t="n">
         <v>27.76496616377404</v>
@@ -6712,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02778295904863626</v>
+        <v>0.02705150004476309</v>
       </c>
       <c r="C2" t="n">
         <v>21.00903377543665</v>
@@ -6794,7 +6794,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02431704197078943</v>
+        <v>0.02372220804682001</v>
       </c>
       <c r="C2" t="n">
         <v>22.5923247955346</v>
@@ -6876,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02818900003330782</v>
+        <v>0.04063112504081801</v>
       </c>
       <c r="C2" t="n">
         <v>27.88696938816474</v>
@@ -6958,7 +6958,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02522391697857529</v>
+        <v>0.0246574169723317</v>
       </c>
       <c r="C2" t="n">
         <v>21.86986697527956</v>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02978179103229195</v>
+        <v>0.03028616699157283</v>
       </c>
       <c r="C2" t="n">
         <v>22.7983048366498</v>
@@ -7122,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02558195899473503</v>
+        <v>0.02662887499900535</v>
       </c>
       <c r="C2" t="n">
         <v>24.55290398302027</v>
@@ -7204,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02285150001989678</v>
+        <v>0.02309679199242964</v>
       </c>
       <c r="C2" t="n">
         <v>21.97671183801047</v>
@@ -7286,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02613937499700114</v>
+        <v>0.02579512499505654</v>
       </c>
       <c r="C2" t="n">
         <v>19.11557092553943</v>
@@ -7368,7 +7368,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02270054101245478</v>
+        <v>0.02397270803339779</v>
       </c>
       <c r="C2" t="n">
         <v>18.50144088898948</v>
@@ -7450,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02567474998068064</v>
+        <v>0.02504316699923947</v>
       </c>
       <c r="C2" t="n">
         <v>24.20842612192556</v>
@@ -7532,7 +7532,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0215961670037359</v>
+        <v>0.02129658398916945</v>
       </c>
       <c r="C2" t="n">
         <v>23.71433253618834</v>
@@ -7614,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02781754202442244</v>
+        <v>0.02801612502662465</v>
       </c>
       <c r="C2" t="n">
         <v>22.34129119357891</v>
@@ -7696,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03214366600150242</v>
+        <v>0.03372850001323968</v>
       </c>
       <c r="C2" t="n">
         <v>25.05896833461931</v>
@@ -7778,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0320017909980379</v>
+        <v>0.03101445798529312</v>
       </c>
       <c r="C2" t="n">
         <v>26.11011028306422</v>
@@ -7860,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0298285839962773</v>
+        <v>0.02932083298219368</v>
       </c>
       <c r="C2" t="n">
         <v>33.43400446309265</v>
@@ -7942,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03138875000877306</v>
+        <v>0.03034300002036616</v>
       </c>
       <c r="C2" t="n">
         <v>22.47006814094689</v>
@@ -8024,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03208912501577288</v>
+        <v>0.03282512497389689</v>
       </c>
       <c r="C2" t="n">
         <v>22.46071232250678</v>
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03009299997938797</v>
+        <v>0.02883758302778006</v>
       </c>
       <c r="C2" t="n">
         <v>22.8529942736679</v>
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02531758398981765</v>
+        <v>0.02508187503553927</v>
       </c>
       <c r="C2" t="n">
         <v>19.74744224621135</v>
@@ -8270,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03277570899808779</v>
+        <v>0.034128499974031</v>
       </c>
       <c r="C2" t="n">
         <v>22.17746432920563</v>
@@ -8352,7 +8352,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02131770900450647</v>
+        <v>0.02054620900889859</v>
       </c>
       <c r="C2" t="n">
         <v>21.34317608906629</v>
@@ -8434,7 +8434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02717120799934492</v>
+        <v>0.02560979197733104</v>
       </c>
       <c r="C2" t="n">
         <v>22.23178981510674</v>
@@ -8516,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02273395896190777</v>
+        <v>0.02163216704502702</v>
       </c>
       <c r="C2" t="n">
         <v>24.47429736964125</v>
@@ -8598,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02966895798454061</v>
+        <v>0.02926754101645201</v>
       </c>
       <c r="C2" t="n">
         <v>21.30842460303775</v>
@@ -8680,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02774366701487452</v>
+        <v>0.02726070798235014</v>
       </c>
       <c r="C2" t="n">
         <v>29.81817504558553</v>

--- a/results/greedy/UAVs6_GRID13/revenue/UAVs6_GRID13_Greedy.xlsx
+++ b/results/greedy/UAVs6_GRID13/revenue/UAVs6_GRID13_Greedy.xlsx
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0275510840001516</v>
+        <v>0.02755733398953453</v>
       </c>
       <c r="C2" t="n">
         <v>22.03601984821984</v>
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.029060082975775</v>
+        <v>0.02828637498896569</v>
       </c>
       <c r="C2" t="n">
         <v>29.28950278519935</v>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02896591601893306</v>
+        <v>0.02869045798433945</v>
       </c>
       <c r="C2" t="n">
         <v>18.35190168986177</v>
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02519029099494219</v>
+        <v>0.02499345800606534</v>
       </c>
       <c r="C2" t="n">
         <v>23.15638464690869</v>
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02998950000619516</v>
+        <v>0.02973050001310185</v>
       </c>
       <c r="C2" t="n">
         <v>33.65493619585379</v>
@@ -972,7 +972,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03044012497412041</v>
+        <v>0.02997870795661584</v>
       </c>
       <c r="C2" t="n">
         <v>30.35759085654207</v>
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02990545897046104</v>
+        <v>0.02993004204472527</v>
       </c>
       <c r="C2" t="n">
         <v>30.02368335018279</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02715791697846726</v>
+        <v>0.02708804199937731</v>
       </c>
       <c r="C2" t="n">
         <v>28.82881202592714</v>
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02997070801211521</v>
+        <v>0.02979695901740342</v>
       </c>
       <c r="C2" t="n">
         <v>32.12904001494914</v>
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0320966670406051</v>
+        <v>0.03204587497748435</v>
       </c>
       <c r="C2" t="n">
         <v>22.0618633491888</v>
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02213308302452788</v>
+        <v>0.02203879103763029</v>
       </c>
       <c r="C2" t="n">
         <v>28.25870754107827</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02938554203137755</v>
+        <v>0.02924466598778963</v>
       </c>
       <c r="C2" t="n">
         <v>25.1241342173652</v>
@@ -1546,7 +1546,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02459899999666959</v>
+        <v>0.024542500032112</v>
       </c>
       <c r="C2" t="n">
         <v>25.59595959784506</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02867737499764189</v>
+        <v>0.02895883400924504</v>
       </c>
       <c r="C2" t="n">
         <v>19.90124277938915</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02806012501241639</v>
+        <v>0.027952250035014</v>
       </c>
       <c r="C2" t="n">
         <v>18.29892475334922</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03133200004231185</v>
+        <v>0.03117195802042261</v>
       </c>
       <c r="C2" t="n">
         <v>23.35471121474562</v>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02627416700124741</v>
+        <v>0.02581083303084597</v>
       </c>
       <c r="C2" t="n">
         <v>23.14833995101325</v>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02515916700940579</v>
+        <v>0.02495608403114602</v>
       </c>
       <c r="C2" t="n">
         <v>16.79384373948809</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02558374998625368</v>
+        <v>0.02532866696128622</v>
       </c>
       <c r="C2" t="n">
         <v>18.48671267501164</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02388908399734646</v>
+        <v>0.02378091699210927</v>
       </c>
       <c r="C2" t="n">
         <v>23.58000159949182</v>
@@ -2202,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02579054201487452</v>
+        <v>0.02578399999765679</v>
       </c>
       <c r="C2" t="n">
         <v>21.82405981796242</v>
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02694612502818927</v>
+        <v>0.02715745801106095</v>
       </c>
       <c r="C2" t="n">
         <v>25.99346061631328</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02840050001395866</v>
+        <v>0.02872529096202925</v>
       </c>
       <c r="C2" t="n">
         <v>24.93305602091468</v>
@@ -2448,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02285841701086611</v>
+        <v>0.02205320802750066</v>
       </c>
       <c r="C2" t="n">
         <v>21.92307197526525</v>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02288550004595891</v>
+        <v>0.0226876669912599</v>
       </c>
       <c r="C2" t="n">
         <v>21.97749828921184</v>
@@ -2612,7 +2612,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0240295419935137</v>
+        <v>0.02407508401665837</v>
       </c>
       <c r="C2" t="n">
         <v>17.17916472768112</v>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02483004203531891</v>
+        <v>0.02479741699062288</v>
       </c>
       <c r="C2" t="n">
         <v>24.1167609262199</v>
@@ -2776,7 +2776,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02422020799713209</v>
+        <v>0.02385004103416577</v>
       </c>
       <c r="C2" t="n">
         <v>22.54436730414327</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02501554199261591</v>
+        <v>0.02524904196616262</v>
       </c>
       <c r="C2" t="n">
         <v>17.3115732314635</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02251079102279618</v>
+        <v>0.02236854197690263</v>
       </c>
       <c r="C2" t="n">
         <v>23.73936112239397</v>
@@ -3022,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02998737496091053</v>
+        <v>0.02994375000707805</v>
       </c>
       <c r="C2" t="n">
         <v>19.73151194935742</v>
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02770108298864216</v>
+        <v>0.02828812500229105</v>
       </c>
       <c r="C2" t="n">
         <v>23.97840807485265</v>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02731404203223065</v>
+        <v>0.02752545895054936</v>
       </c>
       <c r="C2" t="n">
         <v>27.92081469807493</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01968445797683671</v>
+        <v>0.01977750001242384</v>
       </c>
       <c r="C2" t="n">
         <v>21.78805973476554</v>
@@ -3350,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02241412497824058</v>
+        <v>0.02261337504023686</v>
       </c>
       <c r="C2" t="n">
         <v>27.24171464813199</v>
@@ -3432,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02500183403026313</v>
+        <v>0.02485266700387001</v>
       </c>
       <c r="C2" t="n">
         <v>24.5433041426314</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02460491703823209</v>
+        <v>0.02436800004215911</v>
       </c>
       <c r="C2" t="n">
         <v>22.55873961400847</v>
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03423070901772007</v>
+        <v>0.03459945798385888</v>
       </c>
       <c r="C2" t="n">
         <v>21.6712897109124</v>
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0272982909809798</v>
+        <v>0.02705958299338818</v>
       </c>
       <c r="C2" t="n">
         <v>23.11584874919498</v>
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02249549998668954</v>
+        <v>0.02210050000576302</v>
       </c>
       <c r="C2" t="n">
         <v>24.4905058147199</v>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02186662500025705</v>
+        <v>0.02191974996821955</v>
       </c>
       <c r="C2" t="n">
         <v>21.79880306478124</v>
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02725995797663927</v>
+        <v>0.02767891599796712</v>
       </c>
       <c r="C2" t="n">
         <v>18.34277641864116</v>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02183670795056969</v>
+        <v>0.02188141603255644</v>
       </c>
       <c r="C2" t="n">
         <v>17.93794044029475</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03245666698785499</v>
+        <v>0.03229979198658839</v>
       </c>
       <c r="C2" t="n">
         <v>22.35116108760516</v>
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02913016703678295</v>
+        <v>0.02872475003823638</v>
       </c>
       <c r="C2" t="n">
         <v>20.50354395569286</v>
@@ -4252,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0291592919966206</v>
+        <v>0.02910008298931643</v>
       </c>
       <c r="C2" t="n">
         <v>28.61556256222276</v>
@@ -4334,7 +4334,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02697312500094995</v>
+        <v>0.02669141598744318</v>
       </c>
       <c r="C2" t="n">
         <v>24.88746867068073</v>
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02330291602993384</v>
+        <v>0.02336712501710281</v>
       </c>
       <c r="C2" t="n">
         <v>24.46830807390545</v>
@@ -4498,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03440866596065462</v>
+        <v>0.03441462496994063</v>
       </c>
       <c r="C2" t="n">
         <v>22.95319995980014</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0221745420130901</v>
+        <v>0.02217466704314575</v>
       </c>
       <c r="C2" t="n">
         <v>21.89647686035734</v>
@@ -4662,7 +4662,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02480949996970594</v>
+        <v>0.02473520900821313</v>
       </c>
       <c r="C2" t="n">
         <v>22.02114914635661</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03213399997912347</v>
+        <v>0.03165950003312901</v>
       </c>
       <c r="C2" t="n">
         <v>20.65073803524404</v>
@@ -4826,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02047841699095443</v>
+        <v>0.02059241698589176</v>
       </c>
       <c r="C2" t="n">
         <v>23.97437968876231</v>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03150616702623665</v>
+        <v>0.03202633402543142</v>
       </c>
       <c r="C2" t="n">
         <v>18.9863261839787</v>
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02212233399040997</v>
+        <v>0.02224858297267929</v>
       </c>
       <c r="C2" t="n">
         <v>30.07226733260812</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02182029199320823</v>
+        <v>0.02185983402887359</v>
       </c>
       <c r="C2" t="n">
         <v>27.33366989088363</v>
@@ -5154,7 +5154,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02853287500329316</v>
+        <v>0.02861116698477417</v>
       </c>
       <c r="C2" t="n">
         <v>28.13257346125701</v>
@@ -5236,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0265000420040451</v>
+        <v>0.02665133395930752</v>
       </c>
       <c r="C2" t="n">
         <v>26.22672285991993</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02401812502648681</v>
+        <v>0.02375087502878159</v>
       </c>
       <c r="C2" t="n">
         <v>19.62577991293459</v>
@@ -5400,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02911466598743573</v>
+        <v>0.02924829197581857</v>
       </c>
       <c r="C2" t="n">
         <v>22.98857844681716</v>
@@ -5482,7 +5482,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02613087499048561</v>
+        <v>0.02636399999028072</v>
       </c>
       <c r="C2" t="n">
         <v>24.19647588320612</v>
@@ -5564,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02203629101859406</v>
+        <v>0.02229129202896729</v>
       </c>
       <c r="C2" t="n">
         <v>26.58613951306989</v>
@@ -5646,7 +5646,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02797604200895876</v>
+        <v>0.02816625003470108</v>
       </c>
       <c r="C2" t="n">
         <v>21.92262512073578</v>
@@ -5728,7 +5728,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02559224999276921</v>
+        <v>0.02592591696884483</v>
       </c>
       <c r="C2" t="n">
         <v>21.37627224811055</v>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02802262495970353</v>
+        <v>0.02770224999403581</v>
       </c>
       <c r="C2" t="n">
         <v>27.88925930542947</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01814066700171679</v>
+        <v>0.01817208295688033</v>
       </c>
       <c r="C2" t="n">
         <v>19.40025253135037</v>
@@ -5974,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02750108402688056</v>
+        <v>0.02831200003856793</v>
       </c>
       <c r="C2" t="n">
         <v>15.21854064045392</v>
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02598204195965081</v>
+        <v>0.02540887502254918</v>
       </c>
       <c r="C2" t="n">
         <v>22.01653936917196</v>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03146958304569125</v>
+        <v>0.03103662497596815</v>
       </c>
       <c r="C2" t="n">
         <v>19.2609311307482</v>
@@ -6220,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03326870797900483</v>
+        <v>0.03305841697147116</v>
       </c>
       <c r="C2" t="n">
         <v>22.74616692007795</v>
@@ -6302,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03029316599713638</v>
+        <v>0.03031791601097211</v>
       </c>
       <c r="C2" t="n">
         <v>28.75834142897775</v>
@@ -6384,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03341795899905264</v>
+        <v>0.03365245898021385</v>
       </c>
       <c r="C2" t="n">
         <v>27.68072824292527</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02540375001262873</v>
+        <v>0.025476458016783</v>
       </c>
       <c r="C2" t="n">
         <v>24.51982953038614</v>
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02334874996449798</v>
+        <v>0.02364291698904708</v>
       </c>
       <c r="C2" t="n">
         <v>15.94961257308852</v>
@@ -6630,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01926079200347885</v>
+        <v>0.01921608304837719</v>
       </c>
       <c r="C2" t="n">
         <v>27.76496616377404</v>
@@ -6712,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02705150004476309</v>
+        <v>0.0271868749987334</v>
       </c>
       <c r="C2" t="n">
         <v>21.00903377543665</v>
@@ -6794,7 +6794,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02372220804682001</v>
+        <v>0.02378791698720306</v>
       </c>
       <c r="C2" t="n">
         <v>22.5923247955346</v>
@@ -6876,7 +6876,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04063112504081801</v>
+        <v>0.02726729097776115</v>
       </c>
       <c r="C2" t="n">
         <v>27.88696938816474</v>
@@ -6958,7 +6958,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0246574169723317</v>
+        <v>0.02448241703677922</v>
       </c>
       <c r="C2" t="n">
         <v>21.86986697527956</v>
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03028616699157283</v>
+        <v>0.02945349999936298</v>
       </c>
       <c r="C2" t="n">
         <v>22.7983048366498</v>
@@ -7122,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02662887499900535</v>
+        <v>0.02479633403709158</v>
       </c>
       <c r="C2" t="n">
         <v>24.55290398302027</v>
@@ -7204,7 +7204,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02309679199242964</v>
+        <v>0.02232083299895748</v>
       </c>
       <c r="C2" t="n">
         <v>21.97671183801047</v>
@@ -7286,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02579512499505654</v>
+        <v>0.02587308298097923</v>
       </c>
       <c r="C2" t="n">
         <v>19.11557092553943</v>
@@ -7368,7 +7368,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02397270803339779</v>
+        <v>0.02228779101278633</v>
       </c>
       <c r="C2" t="n">
         <v>18.50144088898948</v>
@@ -7450,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02504316699923947</v>
+        <v>0.0251517909928225</v>
       </c>
       <c r="C2" t="n">
         <v>24.20842612192556</v>
@@ -7532,7 +7532,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02129658398916945</v>
+        <v>0.02097833302104846</v>
       </c>
       <c r="C2" t="n">
         <v>23.71433253618834</v>
@@ -7614,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02801612502662465</v>
+        <v>0.02748600003542379</v>
       </c>
       <c r="C2" t="n">
         <v>22.34129119357891</v>
@@ -7696,7 +7696,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03372850001323968</v>
+        <v>0.03177649999270216</v>
       </c>
       <c r="C2" t="n">
         <v>25.05896833461931</v>
@@ -7778,7 +7778,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03101445798529312</v>
+        <v>0.03078141703736037</v>
       </c>
       <c r="C2" t="n">
         <v>26.11011028306422</v>
@@ -7860,7 +7860,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02932083298219368</v>
+        <v>0.02893754199612886</v>
       </c>
       <c r="C2" t="n">
         <v>33.43400446309265</v>
@@ -7942,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03034300002036616</v>
+        <v>0.03007224999601021</v>
       </c>
       <c r="C2" t="n">
         <v>22.47006814094689</v>
@@ -8024,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03282512497389689</v>
+        <v>0.03178312495583668</v>
       </c>
       <c r="C2" t="n">
         <v>22.46071232250678</v>
@@ -8106,7 +8106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02883758302778006</v>
+        <v>0.02954279200639576</v>
       </c>
       <c r="C2" t="n">
         <v>22.8529942736679</v>
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02508187503553927</v>
+        <v>0.02561250003054738</v>
       </c>
       <c r="C2" t="n">
         <v>19.74744224621135</v>
@@ -8270,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.034128499974031</v>
+        <v>0.03307758399751037</v>
       </c>
       <c r="C2" t="n">
         <v>22.17746432920563</v>
@@ -8352,7 +8352,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02054620900889859</v>
+        <v>0.02023070800350979</v>
       </c>
       <c r="C2" t="n">
         <v>21.34317608906629</v>
@@ -8434,7 +8434,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02560979197733104</v>
+        <v>0.02550645801238716</v>
       </c>
       <c r="C2" t="n">
         <v>22.23178981510674</v>
@@ -8516,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02163216704502702</v>
+        <v>0.02126108400989324</v>
       </c>
       <c r="C2" t="n">
         <v>24.47429736964125</v>
@@ -8598,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02926754101645201</v>
+        <v>0.0285469579976052</v>
       </c>
       <c r="C2" t="n">
         <v>21.30842460303775</v>
@@ -8680,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02726070798235014</v>
+        <v>0.02685833297437057</v>
       </c>
       <c r="C2" t="n">
         <v>29.81817504558553</v>
